--- a/data/trans_orig/IP07C17-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C17-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29653</t>
+          <t>29711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45154</t>
+          <t>45883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25822</t>
+          <t>25411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41748</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59242</t>
+          <t>59758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81100</t>
+          <t>82162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42720</t>
+          <t>42797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58883</t>
+          <t>59548</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34945</t>
+          <t>34952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>52334</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83427</t>
+          <t>82397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107352</t>
+          <t>106729</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12686</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25601</t>
+          <t>24712</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24022</t>
+          <t>23179</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38835</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40476</t>
+          <t>39749</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60236</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>36825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56418</t>
+          <t>56004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24192</t>
+          <t>24301</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40786</t>
+          <t>41398</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66961</t>
+          <t>66470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90978</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69761</t>
+          <t>69406</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89601</t>
+          <t>90420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61693</t>
+          <t>61917</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82597</t>
+          <t>82712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139104</t>
+          <t>137161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167823</t>
+          <t>167803</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44081</t>
+          <t>43977</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52326</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72803</t>
+          <t>71541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82530</t>
+          <t>82759</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109914</t>
+          <t>111357</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16005</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27395</t>
+          <t>26655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27957</t>
+          <t>27635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>71501</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>95815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53626</t>
+          <t>54046</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76799</t>
+          <t>76261</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131401</t>
+          <t>132584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164837</t>
+          <t>166964</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116210</t>
+          <t>116890</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144178</t>
+          <t>144807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102097</t>
+          <t>102775</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>128394</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227655</t>
+          <t>227618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266108</t>
+          <t>266085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>42339</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63346</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79686</t>
+          <t>79948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105234</t>
+          <t>105658</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>130913</t>
+          <t>128052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164314</t>
+          <t>162636</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23309</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>17225</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38634</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56386</t>
+          <t>56057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75722</t>
+          <t>75470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48347</t>
+          <t>49048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68031</t>
+          <t>67996</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111016</t>
+          <t>110450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137893</t>
+          <t>138014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46610</t>
+          <t>46564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66436</t>
+          <t>65703</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46864</t>
+          <t>46854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66308</t>
+          <t>66610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99986</t>
+          <t>98556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127150</t>
+          <t>126678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,66%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>28546</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16969</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31443</t>
+          <t>31889</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34316</t>
+          <t>34981</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55247</t>
+          <t>54596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23114</t>
+          <t>23635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42769</t>
+          <t>43407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62264</t>
+          <t>62344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40019</t>
+          <t>40241</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59688</t>
+          <t>59522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88537</t>
+          <t>89073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116543</t>
+          <t>117746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67696</t>
+          <t>67866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>49398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68531</t>
+          <t>69859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102343</t>
+          <t>102376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131150</t>
+          <t>131059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47788</t>
+          <t>46891</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>33158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52159</t>
+          <t>51653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65809</t>
+          <t>66057</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>90950</t>
+          <t>90769</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12496</t>
+          <t>13175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16161</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24839</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24218</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>104600</t>
+          <t>105430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132757</t>
+          <t>132903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94179</t>
+          <t>91624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122069</t>
+          <t>121567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206927</t>
+          <t>205937</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>246981</t>
+          <t>247934</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100780</t>
+          <t>99071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127580</t>
+          <t>128486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100838</t>
+          <t>101430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130016</t>
+          <t>129835</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207403</t>
+          <t>208681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>247616</t>
+          <t>249088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46179</t>
+          <t>46144</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67586</t>
+          <t>69547</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54481</t>
+          <t>55101</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79442</t>
+          <t>79226</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>105338</t>
+          <t>106391</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>138847</t>
+          <t>137411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28119</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25019</t>
+          <t>24852</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44637</t>
+          <t>43091</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>23063</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35025</t>
+          <t>32647</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2016 (tasa de respuesta: 95,57%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2016 (tasa de respuesta: 95,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64850</t>
+          <t>63776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85352</t>
+          <t>85560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57469</t>
+          <t>56761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79087</t>
+          <t>77718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126130</t>
+          <t>127797</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156954</t>
+          <t>158712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57909</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79351</t>
+          <t>79959</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57925</t>
+          <t>58105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79830</t>
+          <t>78867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120432</t>
+          <t>121790</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152895</t>
+          <t>152782</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17490</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>32255</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>18185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>34307</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39427</t>
+          <t>39808</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61190</t>
+          <t>61650</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>17719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26239</t>
+          <t>27230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>17614</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59172</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47899</t>
+          <t>47354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72615</t>
+          <t>73264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100273</t>
+          <t>98654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53165</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74496</t>
+          <t>75718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62685</t>
+          <t>61858</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84467</t>
+          <t>83763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122386</t>
+          <t>122764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151823</t>
+          <t>154380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26654</t>
+          <t>27182</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43950</t>
+          <t>44453</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>37136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56427</t>
+          <t>56061</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69067</t>
+          <t>68629</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>94619</t>
+          <t>93742</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19889</t>
+          <t>18893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109354</t>
+          <t>108933</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138006</t>
+          <t>138204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90126</t>
+          <t>91587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118410</t>
+          <t>120178</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207309</t>
+          <t>209057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247274</t>
+          <t>249318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117067</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146554</t>
+          <t>147006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127357</t>
+          <t>127977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>157520</t>
+          <t>158094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254266</t>
+          <t>251008</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297069</t>
+          <t>295886</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48050</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70161</t>
+          <t>71175</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>59817</t>
+          <t>60416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85350</t>
+          <t>85433</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114154</t>
+          <t>114904</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>147919</t>
+          <t>148096</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>26269</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>48002</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32282</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C17-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C17-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de gustarle ir al colegio en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio, percibida por el/la menor en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33062</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26203</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42773</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>37092</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29711</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45883</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>29754</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>46043</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>33,2%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>33062</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>25411</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>42071</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>26,93%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59758</t>
+          <t>58985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82162</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43486</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35546</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>52651</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>50978</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42797</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>59548</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42201</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>59272</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>45,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>43486</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>34952</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>52334</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82397</t>
+          <t>82505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106729</t>
+          <t>106889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30897</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23717</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38458</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>25,16%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>31,32%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18367</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12009</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24712</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12612</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>25934</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>16,44%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>30897</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>23179</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>38835</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39749</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59836</t>
+          <t>58870</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3418</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11773</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3820</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1422</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7838</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6306</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2916</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11311</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>17080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9036</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5441</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14684</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1453</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5804</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5039</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>9036</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5085</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>14414</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122787</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122787</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122787</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122787</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>122787</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>122787</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32055</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24473</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40649</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>46217</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>36825</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56004</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37238</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56574</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>25,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>32055</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>24301</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>41398</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,22%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66470</t>
+          <t>66753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90680</t>
+          <t>92338</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72163</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>62115</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>83044</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>80049</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>69406</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>90420</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>69643</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>91710</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>44,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>38,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>72163</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61917</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>82712</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>38,78%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>136995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167803</t>
+          <t>167674</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61858</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>51747</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73325</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>33,24%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>27,81%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>34054</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>26445</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>43977</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>25650</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>42734</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>19,03%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>61858</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>51329</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>71541</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>33,24%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82759</t>
+          <t>83375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>111357</t>
+          <t>109872</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10115</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6029</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15812</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9260</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5480</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15263</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5406</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15342</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10115</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6114</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16540</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13157</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9907</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5861</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16455</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>9354</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5349</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14861</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5790</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15741</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>5,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>9907</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5598</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>15930</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>13421</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27635</t>
+          <t>26581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65117</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54529</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77288</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>25,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>83310</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>71501</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>95815</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>71191</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>96271</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>28,66%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>65117</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>54046</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>76261</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132584</t>
+          <t>132060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>166964</t>
+          <t>166124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>115648</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>102711</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>129892</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,25%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>131027</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>116890</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>144807</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>117123</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>145135</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>45,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>40,22%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>49,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>115648</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>102775</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>128394</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227618</t>
+          <t>226473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266085</t>
+          <t>265582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>92755</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>80096</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>104911</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>30,03%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>25,93%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>33,96%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>52422</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>42339</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>63512</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>42711</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>64188</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>18,04%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>92755</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>79948</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>105658</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>30,03%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128052</t>
+          <t>129397</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>162636</t>
+          <t>162463</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16420</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>10650</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>24098</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>13080</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7980</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>19189</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>8015</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>19077</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>4,5%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>16420</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>11027</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>24232</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21556</t>
+          <t>21506</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39480</t>
+          <t>38503</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18943</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12792</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>25946</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>10808</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6416</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>17225</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>6458</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>17277</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>3,72%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>18943</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>13040</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>27336</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39169</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>308884</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>308884</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>308884</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>432</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>308884</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>308884</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>308884</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de gustarle ir al colegio en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio, percibida por el/la menor en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57832</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48014</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>67926</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65881</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>56057</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>75470</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>56291</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>76657</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>44,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>57832</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>49048</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>67996</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110450</t>
+          <t>109515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138014</t>
+          <t>136899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56424</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46292</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>67160</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55791</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46564</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>65703</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>46624</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>65572</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,36%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56424</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>46854</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66610</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98556</t>
+          <t>98707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126678</t>
+          <t>126024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24023</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17186</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32568</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21,04%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>20066</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13978</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>28546</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>13662</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>28004</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,44%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24023</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16555</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>31889</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34981</t>
+          <t>35236</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54596</t>
+          <t>55360</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9948</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5174</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16162</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6233</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2972</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11165</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3203</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11421</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9948</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5682</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16617</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23635</t>
+          <t>24587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6546</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11197</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1368</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4833</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4626</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6546</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3254</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>11356</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154773</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154773</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154773</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149338</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149338</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149338</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154773</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154773</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154773</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49884</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40525</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59721</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>52967</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43407</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62344</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>43192</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>62835</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,78%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>49884</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>40241</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>59522</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>29,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89073</t>
+          <t>89726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117746</t>
+          <t>117210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58246</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48053</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67827</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,36%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>57758</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>47509</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>67866</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>48189</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>68279</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>35,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>58246</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>49398</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69859</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,37%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102376</t>
+          <t>102607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131059</t>
+          <t>130045</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>42009</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33045</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51159</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24,79%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>19,5%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,19%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36279</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>28601</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>46891</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>27601</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>45586</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>22,45%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>29,02%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>42009</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>33158</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>51653</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>24,79%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66057</t>
+          <t>66271</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>90769</t>
+          <t>92226</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10224</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5766</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15956</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7085</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3662</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13175</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3379</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12418</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,38%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10224</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5976</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16546</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9084</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5010</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14489</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>7511</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3906</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12852</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12805</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>4,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>9084</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5375</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14518</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169448</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169448</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169448</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>161600</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>161600</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>161600</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>169448</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>169448</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>169448</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>107716</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>94446</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>122681</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,22%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>37,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>105430</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>132903</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>105068</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>132016</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>38,22%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>107716</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>91624</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>121567</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,22%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>205937</t>
+          <t>209204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247934</t>
+          <t>247866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>114671</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>101413</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>130172</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,28%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>113549</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>99071</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128486</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>99394</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>127162</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>36,52%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>114671</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>101430</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>129835</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,37%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208681</t>
+          <t>207767</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>249088</t>
+          <t>248049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>66032</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>55176</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>78628</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20,37%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>17,02%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>24,25%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>56345</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>46144</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>69547</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>46320</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>67965</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>18,12%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,37%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>66032</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>55101</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>79226</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106391</t>
+          <t>107783</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137411</t>
+          <t>140579</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20173</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13386</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>28587</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>13318</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>8356</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>19885</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>8197</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>4,28%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>20173</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>13902</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>29228</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43091</t>
+          <t>43049</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15631</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10351</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>22189</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>8879</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4836</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>16002</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4562</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>14451</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,86%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>15631</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>10598</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>23063</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32647</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>324222</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>324222</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>324222</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>310938</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>310938</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>310938</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>324222</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>324222</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>324222</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de gustarle ir al colegio en 2016 (tasa de respuesta: 95,57%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio, percibida por el/la menor en 2016 (tasa de respuesta: 95,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>67685</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57207</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>78661</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>44,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>74703</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>63776</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85560</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>64285</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>86831</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>35,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>67685</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>56761</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>77718</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127797</t>
+          <t>126153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158712</t>
+          <t>156875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68745</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57788</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80264</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32,6%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>68269</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57602</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>79959</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>57188</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>79665</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,74%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,2%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68745</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58105</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>78867</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,78%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121790</t>
+          <t>122588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152782</t>
+          <t>153606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,89%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25419</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18615</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>35401</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,34%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,97%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>23888</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17200</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>32255</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17306</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>32177</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,21%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,83%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>25419</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>18185</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>34307</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39808</t>
+          <t>39002</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61650</t>
+          <t>61075</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -5613,74 +5613,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11264</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6706</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18229</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7204</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12598</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3668</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12588</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,98%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>6,96%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11264</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6713</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17719</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>12689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>27033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -5726,107 +5726,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8167</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6823</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12404</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12571</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>3,77%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4156</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1464</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8760</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>10979</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>6424</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>17695</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>4,94%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>10979</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>6140</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>17614</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>177268</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>177268</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>177268</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>180887</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>177268</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>177268</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>177268</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37192</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28898</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46487</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>48191</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>38605</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59295</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>38801</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>57600</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>37192</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>29047</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>47354</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,8%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73264</t>
+          <t>72501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98654</t>
+          <t>99024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>73715</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>63864</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>85073</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>43,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>63912</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53207</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>75718</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53408</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74279</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,78%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>73715</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61858</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>83763</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>43,21%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122764</t>
+          <t>122751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154380</t>
+          <t>153343</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>46098</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37141</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55538</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>27,02%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>21,77%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>35488</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27182</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>44453</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>27537</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>45012</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>21,53%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>26,97%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>46098</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>37136</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>56061</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>27,02%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>68629</t>
+          <t>69747</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>93742</t>
+          <t>94522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6932</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11901</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11164</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6242</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17494</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7016</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17498</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6932</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3483</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12620</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>25255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -6413,67 +6413,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12333</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>6051</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2809</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10877</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11498</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6654</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3113</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>12011</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>20468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>104877</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>91197</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>118798</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30,15%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>122894</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>108933</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>138204</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>108819</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>138469</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>104877</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>91587</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>120178</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>30,15%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209057</t>
+          <t>206796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249318</t>
+          <t>248793</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>142460</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>126448</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>157695</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,95%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>132181</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>117083</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>147006</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>118146</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>147573</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>142460</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>127977</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>158094</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,95%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251008</t>
+          <t>252851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>295886</t>
+          <t>296449</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>71517</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>59229</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>84424</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20,56%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>17,03%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>59376</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>48006</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>71175</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>48188</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>72148</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>17,18%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,59%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>71517</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>60416</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>85433</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114904</t>
+          <t>113674</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>148096</t>
+          <t>148518</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>18196</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11981</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>25789</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>18369</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>12090</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>26269</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>12155</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>26170</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>5,31%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>18196</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>12441</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>27065</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27821</t>
+          <t>27380</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48002</t>
+          <t>46787</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10810</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6014</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>12874</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7530</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19186</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>7536</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>19452</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>3,72%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>2,18%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10810</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>6270</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>17464</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32527</t>
+          <t>32425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>347860</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>347860</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>347860</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>345694</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>345694</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>345694</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>347860</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>347860</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>347860</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
